--- a/examples/segment/Thornhill_Segment_Config.xlsx
+++ b/examples/segment/Thornhill_Segment_Config.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t xml:space="preserve">Setting</t>
   </si>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">analyst_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Turas worked example</t>
+    <t xml:space="preserve">Example analyst</t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
@@ -262,6 +262,12 @@
   </si>
   <si>
     <t xml:space="preserve">The Research LampPost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thornhill Grocers</t>
   </si>
   <si>
     <t xml:space="preserve">Variable</t>
@@ -1051,6 +1057,14 @@
         <v>82</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B52" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1068,58 +1082,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/examples/segment/Thornhill_Segment_Config.xlsx
+++ b/examples/segment/Thornhill_Segment_Config.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t xml:space="preserve">Setting</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tabs_export</t>
   </si>
   <si>
     <t xml:space="preserve">segment_names</t>
@@ -838,23 +841,23 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
         <v>47</v>
-      </c>
-      <c r="B25" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
         <v>49</v>
-      </c>
-      <c r="B26" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="27">
@@ -862,7 +865,7 @@
         <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -870,31 +873,31 @@
         <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
         <v>53</v>
-      </c>
-      <c r="B29" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
         <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
         <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -990,7 +993,7 @@
         <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
@@ -998,7 +1001,7 @@
         <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
@@ -1014,15 +1017,15 @@
         <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" t="s">
         <v>74</v>
-      </c>
-      <c r="B47" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="48">
@@ -1030,39 +1033,47 @@
         <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" t="s">
         <v>77</v>
-      </c>
-      <c r="B49" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" t="s">
         <v>79</v>
-      </c>
-      <c r="B50" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" t="s">
         <v>81</v>
-      </c>
-      <c r="B51" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" t="s">
         <v>83</v>
       </c>
-      <c r="B52" t="s">
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
         <v>84</v>
+      </c>
+      <c r="B53" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1082,58 +1093,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/examples/segment/Thornhill_Segment_Config.xlsx
+++ b/examples/segment/Thornhill_Segment_Config.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">k_selection_metrics</t>
   </si>
   <si>
-    <t xml:space="preserve">silhouette,elbow</t>
+    <t xml:space="preserve">silhouette,elbow,calinski_harabasz,davies_bouldin</t>
   </si>
   <si>
     <t xml:space="preserve">nstart</t>
